--- a/scratch/가스공사_의뢰서_테스트.xlsx
+++ b/scratch/가스공사_의뢰서_테스트.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6월5일-1" sheetId="1" state="visible" r:id="rId1"/>
@@ -99,11 +99,11 @@
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;4303 - &quot;000"/>
     <numFmt numFmtId="165" formatCode="0\ /\ 0"/>
-    <numFmt numFmtId="166" formatCode="yyyy\.mm\.dd"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="000"/>
-    <numFmt numFmtId="169" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="170" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="168" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
+    <numFmt numFmtId="169" formatCode="yyyy\.mm\.dd"/>
+    <numFmt numFmtId="170" formatCode="000"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -207,7 +207,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -216,17 +216,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -378,32 +367,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -621,6 +588,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -629,91 +626,61 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -728,632 +695,230 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1453,12 +1018,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1">
-          <clrChange>
-            <clrFrom/>
-            <clrTo/>
-          </clrChange>
-        </a:blip>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1502,12 +1062,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2">
-          <clrChange>
-            <clrFrom/>
-            <clrTo/>
-          </clrChange>
-        </a:blip>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -2415,91 +1970,91 @@
     <col width="10.09765625" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="4">
-      <c r="A1" s="181" t="inlineStr">
+    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="44">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>용접 및 비파괴 검사 기록서</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
-      <c r="J1" s="182" t="n"/>
-      <c r="K1" s="182" t="n"/>
-      <c r="L1" s="182" t="n"/>
-      <c r="M1" s="182" t="n"/>
-      <c r="N1" s="182" t="n"/>
-      <c r="O1" s="182" t="n"/>
-      <c r="P1" s="183" t="n"/>
-      <c r="Q1" s="184" t="inlineStr">
+      <c r="B1" s="76" t="n"/>
+      <c r="C1" s="76" t="n"/>
+      <c r="D1" s="76" t="n"/>
+      <c r="E1" s="76" t="n"/>
+      <c r="F1" s="76" t="n"/>
+      <c r="G1" s="76" t="n"/>
+      <c r="H1" s="76" t="n"/>
+      <c r="I1" s="76" t="n"/>
+      <c r="J1" s="76" t="n"/>
+      <c r="K1" s="76" t="n"/>
+      <c r="L1" s="76" t="n"/>
+      <c r="M1" s="76" t="n"/>
+      <c r="N1" s="76" t="n"/>
+      <c r="O1" s="76" t="n"/>
+      <c r="P1" s="77" t="n"/>
+      <c r="Q1" s="100" t="inlineStr">
         <is>
           <t xml:space="preserve">일련번호 : </t>
         </is>
       </c>
-      <c r="R1" s="185" t="n"/>
-      <c r="S1" s="185" t="n"/>
-      <c r="T1" s="186" t="n">
+      <c r="R1" s="101" t="n"/>
+      <c r="S1" s="101" t="n"/>
+      <c r="T1" s="102" t="n">
         <v>1</v>
       </c>
-      <c r="U1" s="187" t="n"/>
-      <c r="V1" s="185" t="n"/>
-      <c r="W1" s="185" t="n"/>
-      <c r="X1" s="185" t="n"/>
-      <c r="Y1" s="185" t="n"/>
-      <c r="Z1" s="185" t="n"/>
-      <c r="AA1" s="185" t="n"/>
-      <c r="AB1" s="188" t="n"/>
+      <c r="U1" s="95" t="n"/>
+      <c r="V1" s="101" t="n"/>
+      <c r="W1" s="101" t="n"/>
+      <c r="X1" s="101" t="n"/>
+      <c r="Y1" s="101" t="n"/>
+      <c r="Z1" s="101" t="n"/>
+      <c r="AA1" s="101" t="n"/>
+      <c r="AB1" s="103" t="n"/>
     </row>
-    <row r="2" ht="19.5" customFormat="1" customHeight="1" s="4">
-      <c r="A2" s="189" t="n"/>
-      <c r="B2" s="190" t="n"/>
-      <c r="C2" s="190" t="n"/>
-      <c r="D2" s="190" t="n"/>
-      <c r="E2" s="190" t="n"/>
-      <c r="F2" s="190" t="n"/>
-      <c r="G2" s="190" t="n"/>
-      <c r="H2" s="190" t="n"/>
-      <c r="I2" s="190" t="n"/>
-      <c r="J2" s="190" t="n"/>
-      <c r="K2" s="190" t="n"/>
-      <c r="L2" s="190" t="n"/>
-      <c r="M2" s="190" t="n"/>
-      <c r="N2" s="190" t="n"/>
-      <c r="O2" s="190" t="n"/>
-      <c r="P2" s="191" t="n"/>
-      <c r="Q2" s="170" t="inlineStr">
+    <row r="2" ht="19.5" customFormat="1" customHeight="1" s="44">
+      <c r="A2" s="57" t="n"/>
+      <c r="B2" s="49" t="n"/>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="49" t="n"/>
+      <c r="K2" s="49" t="n"/>
+      <c r="L2" s="49" t="n"/>
+      <c r="M2" s="49" t="n"/>
+      <c r="N2" s="49" t="n"/>
+      <c r="O2" s="49" t="n"/>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="79" t="inlineStr">
         <is>
           <t>페 이 지 :</t>
         </is>
       </c>
-      <c r="R2" s="192" t="n"/>
-      <c r="S2" s="192" t="n"/>
-      <c r="T2" s="192" t="n"/>
-      <c r="U2" s="193" t="n"/>
-      <c r="V2" s="194" t="n">
+      <c r="R2" s="59" t="n"/>
+      <c r="S2" s="59" t="n"/>
+      <c r="T2" s="59" t="n"/>
+      <c r="U2" s="104" t="n"/>
+      <c r="V2" s="105" t="n">
         <v>1</v>
       </c>
-      <c r="W2" s="192" t="n"/>
-      <c r="X2" s="192" t="n"/>
-      <c r="Y2" s="192" t="n"/>
-      <c r="Z2" s="192" t="n"/>
-      <c r="AA2" s="192" t="n"/>
-      <c r="AB2" s="195" t="n"/>
+      <c r="W2" s="59" t="n"/>
+      <c r="X2" s="59" t="n"/>
+      <c r="Y2" s="59" t="n"/>
+      <c r="Z2" s="59" t="n"/>
+      <c r="AA2" s="59" t="n"/>
+      <c r="AB2" s="66" t="n"/>
     </row>
-    <row r="3" ht="19.5" customFormat="1" customHeight="1" s="4">
+    <row r="3" ht="19.5" customFormat="1" customHeight="1" s="44">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> 시공계약자 : 광진기업㈜ / 안중~평택(지하차도)배관이설공사</t>
         </is>
       </c>
-      <c r="B3" s="178" t="n"/>
-      <c r="C3" s="178" t="n"/>
-      <c r="D3" s="178" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
       <c r="E3" s="8" t="n"/>
       <c r="F3" s="8" t="n"/>
       <c r="G3" s="8" t="n"/>
@@ -2512,300 +2067,300 @@
       <c r="N3" s="8" t="n"/>
       <c r="O3" s="8" t="n"/>
       <c r="P3" s="9" t="n"/>
-      <c r="Q3" s="196" t="inlineStr">
+      <c r="Q3" s="97" t="inlineStr">
         <is>
           <t>비파괴검사 용역 수행자 : 서울검사㈜</t>
         </is>
       </c>
-      <c r="R3" s="192" t="n"/>
-      <c r="S3" s="192" t="n"/>
-      <c r="T3" s="192" t="n"/>
-      <c r="U3" s="192" t="n"/>
-      <c r="V3" s="192" t="n"/>
-      <c r="W3" s="192" t="n"/>
-      <c r="X3" s="192" t="n"/>
-      <c r="Y3" s="192" t="n"/>
-      <c r="Z3" s="192" t="n"/>
-      <c r="AA3" s="192" t="n"/>
-      <c r="AB3" s="195" t="n"/>
+      <c r="R3" s="59" t="n"/>
+      <c r="S3" s="59" t="n"/>
+      <c r="T3" s="59" t="n"/>
+      <c r="U3" s="59" t="n"/>
+      <c r="V3" s="59" t="n"/>
+      <c r="W3" s="59" t="n"/>
+      <c r="X3" s="59" t="n"/>
+      <c r="Y3" s="59" t="n"/>
+      <c r="Z3" s="59" t="n"/>
+      <c r="AA3" s="59" t="n"/>
+      <c r="AB3" s="66" t="n"/>
     </row>
-    <row r="4" ht="19.5" customFormat="1" customHeight="1" s="4">
-      <c r="A4" s="197" t="inlineStr">
+    <row r="4" ht="19.5" customFormat="1" customHeight="1" s="44">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>용   접   검   사</t>
         </is>
       </c>
-      <c r="B4" s="192" t="n"/>
-      <c r="C4" s="192" t="n"/>
-      <c r="D4" s="192" t="n"/>
-      <c r="E4" s="192" t="n"/>
-      <c r="F4" s="192" t="n"/>
-      <c r="G4" s="192" t="n"/>
-      <c r="H4" s="192" t="n"/>
-      <c r="I4" s="192" t="n"/>
-      <c r="J4" s="192" t="n"/>
-      <c r="K4" s="192" t="n"/>
-      <c r="L4" s="192" t="n"/>
-      <c r="M4" s="192" t="n"/>
-      <c r="N4" s="192" t="n"/>
-      <c r="O4" s="192" t="n"/>
-      <c r="P4" s="198" t="n"/>
-      <c r="Q4" s="199" t="inlineStr">
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="59" t="n"/>
+      <c r="G4" s="59" t="n"/>
+      <c r="H4" s="59" t="n"/>
+      <c r="I4" s="59" t="n"/>
+      <c r="J4" s="59" t="n"/>
+      <c r="K4" s="59" t="n"/>
+      <c r="L4" s="59" t="n"/>
+      <c r="M4" s="59" t="n"/>
+      <c r="N4" s="59" t="n"/>
+      <c r="O4" s="59" t="n"/>
+      <c r="P4" s="60" t="n"/>
+      <c r="Q4" s="65" t="inlineStr">
         <is>
           <t>비 파 괴 검 사</t>
         </is>
       </c>
-      <c r="R4" s="192" t="n"/>
-      <c r="S4" s="192" t="n"/>
-      <c r="T4" s="192" t="n"/>
-      <c r="U4" s="192" t="n"/>
-      <c r="V4" s="192" t="n"/>
-      <c r="W4" s="192" t="n"/>
-      <c r="X4" s="192" t="n"/>
-      <c r="Y4" s="192" t="n"/>
-      <c r="Z4" s="192" t="n"/>
-      <c r="AA4" s="192" t="n"/>
-      <c r="AB4" s="195" t="n"/>
+      <c r="R4" s="59" t="n"/>
+      <c r="S4" s="59" t="n"/>
+      <c r="T4" s="59" t="n"/>
+      <c r="U4" s="59" t="n"/>
+      <c r="V4" s="59" t="n"/>
+      <c r="W4" s="59" t="n"/>
+      <c r="X4" s="59" t="n"/>
+      <c r="Y4" s="59" t="n"/>
+      <c r="Z4" s="59" t="n"/>
+      <c r="AA4" s="59" t="n"/>
+      <c r="AB4" s="66" t="n"/>
     </row>
-    <row r="5" ht="10.5" customFormat="1" customHeight="1" s="4">
-      <c r="A5" s="200" t="inlineStr">
+    <row r="5" ht="10.5" customFormat="1" customHeight="1" s="44">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>도면 번호</t>
         </is>
       </c>
-      <c r="B5" s="201" t="n"/>
-      <c r="C5" s="202" t="inlineStr">
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="96" t="inlineStr">
         <is>
           <t>02-19-P-08-039-03</t>
         </is>
       </c>
-      <c r="D5" s="201" t="n"/>
-      <c r="E5" s="102" t="inlineStr">
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="71" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
       </c>
-      <c r="F5" s="201" t="n"/>
-      <c r="G5" s="117" t="inlineStr">
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   검사 및 요청일자  </t>
         </is>
       </c>
-      <c r="H5" s="203" t="n"/>
-      <c r="I5" s="203" t="n"/>
-      <c r="J5" s="203" t="n"/>
-      <c r="K5" s="203" t="n"/>
-      <c r="L5" s="204" t="n">
+      <c r="H5" s="45" t="n"/>
+      <c r="I5" s="45" t="n"/>
+      <c r="J5" s="45" t="n"/>
+      <c r="K5" s="45" t="n"/>
+      <c r="L5" s="106" t="n">
         <v>45813</v>
       </c>
-      <c r="M5" s="203" t="n"/>
-      <c r="N5" s="203" t="n"/>
-      <c r="O5" s="203" t="n"/>
-      <c r="P5" s="201" t="n"/>
-      <c r="Q5" s="205" t="inlineStr">
+      <c r="M5" s="45" t="n"/>
+      <c r="N5" s="45" t="n"/>
+      <c r="O5" s="45" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t>비파괴 검사 결과 및 일자</t>
         </is>
       </c>
-      <c r="R5" s="203" t="n"/>
-      <c r="S5" s="203" t="n"/>
-      <c r="T5" s="203" t="n"/>
-      <c r="U5" s="203" t="n"/>
-      <c r="V5" s="203" t="n"/>
-      <c r="W5" s="203" t="n"/>
-      <c r="X5" s="201" t="n"/>
-      <c r="Y5" s="206" t="n">
+      <c r="R5" s="45" t="n"/>
+      <c r="S5" s="45" t="n"/>
+      <c r="T5" s="45" t="n"/>
+      <c r="U5" s="45" t="n"/>
+      <c r="V5" s="45" t="n"/>
+      <c r="W5" s="45" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="107" t="n">
         <v>45813</v>
       </c>
-      <c r="Z5" s="203" t="n"/>
-      <c r="AA5" s="203" t="n"/>
-      <c r="AB5" s="207" t="n"/>
+      <c r="Z5" s="45" t="n"/>
+      <c r="AA5" s="45" t="n"/>
+      <c r="AB5" s="54" t="n"/>
     </row>
-    <row r="6" ht="10.5" customFormat="1" customHeight="1" s="4">
-      <c r="A6" s="189" t="n"/>
-      <c r="B6" s="191" t="n"/>
-      <c r="C6" s="208" t="n"/>
-      <c r="D6" s="191" t="n"/>
-      <c r="E6" s="209" t="n"/>
-      <c r="F6" s="210" t="n"/>
-      <c r="G6" s="208" t="n"/>
-      <c r="H6" s="190" t="n"/>
-      <c r="I6" s="190" t="n"/>
-      <c r="J6" s="190" t="n"/>
-      <c r="K6" s="190" t="n"/>
-      <c r="L6" s="208" t="n"/>
-      <c r="M6" s="190" t="n"/>
-      <c r="N6" s="190" t="n"/>
-      <c r="O6" s="190" t="n"/>
-      <c r="P6" s="191" t="n"/>
-      <c r="Q6" s="208" t="n"/>
-      <c r="R6" s="190" t="n"/>
-      <c r="S6" s="190" t="n"/>
-      <c r="T6" s="190" t="n"/>
-      <c r="U6" s="190" t="n"/>
-      <c r="V6" s="190" t="n"/>
-      <c r="W6" s="190" t="n"/>
-      <c r="X6" s="191" t="n"/>
-      <c r="Y6" s="208" t="n"/>
-      <c r="Z6" s="190" t="n"/>
-      <c r="AA6" s="190" t="n"/>
-      <c r="AB6" s="211" t="n"/>
+    <row r="6" ht="10.5" customFormat="1" customHeight="1" s="44">
+      <c r="A6" s="57" t="n"/>
+      <c r="B6" s="50" t="n"/>
+      <c r="C6" s="48" t="n"/>
+      <c r="D6" s="50" t="n"/>
+      <c r="E6" s="47" t="n"/>
+      <c r="F6" s="41" t="n"/>
+      <c r="G6" s="48" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="49" t="n"/>
+      <c r="K6" s="49" t="n"/>
+      <c r="L6" s="48" t="n"/>
+      <c r="M6" s="49" t="n"/>
+      <c r="N6" s="49" t="n"/>
+      <c r="O6" s="49" t="n"/>
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="48" t="n"/>
+      <c r="R6" s="49" t="n"/>
+      <c r="S6" s="49" t="n"/>
+      <c r="T6" s="49" t="n"/>
+      <c r="U6" s="49" t="n"/>
+      <c r="V6" s="49" t="n"/>
+      <c r="W6" s="49" t="n"/>
+      <c r="X6" s="50" t="n"/>
+      <c r="Y6" s="48" t="n"/>
+      <c r="Z6" s="49" t="n"/>
+      <c r="AA6" s="49" t="n"/>
+      <c r="AB6" s="55" t="n"/>
     </row>
-    <row r="7" ht="12" customFormat="1" customHeight="1" s="4">
-      <c r="A7" s="212" t="inlineStr">
+    <row r="7" ht="12" customFormat="1" customHeight="1" s="44">
+      <c r="A7" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">구간(라인)
 번호  </t>
         </is>
       </c>
-      <c r="B7" s="201" t="n"/>
-      <c r="C7" s="213" t="inlineStr">
+      <c r="B7" s="46" t="n"/>
+      <c r="C7" s="68" t="inlineStr">
         <is>
           <t>신설배관</t>
         </is>
       </c>
-      <c r="D7" s="201" t="n"/>
-      <c r="E7" s="104" t="inlineStr">
+      <c r="D7" s="46" t="n"/>
+      <c r="E7" s="52" t="inlineStr">
         <is>
           <t>발췌율(%)</t>
         </is>
       </c>
-      <c r="F7" s="210" t="n"/>
-      <c r="G7" s="214" t="inlineStr">
+      <c r="F7" s="41" t="n"/>
+      <c r="G7" s="70" t="inlineStr">
         <is>
           <t>②시공계약자 용접검사 및 현장안전상태</t>
         </is>
       </c>
-      <c r="H7" s="203" t="n"/>
-      <c r="I7" s="203" t="n"/>
-      <c r="J7" s="203" t="n"/>
-      <c r="K7" s="201" t="n"/>
-      <c r="L7" s="102" t="n"/>
-      <c r="M7" s="102" t="inlineStr">
+      <c r="H7" s="45" t="n"/>
+      <c r="I7" s="45" t="n"/>
+      <c r="J7" s="45" t="n"/>
+      <c r="K7" s="46" t="n"/>
+      <c r="L7" s="71" t="n"/>
+      <c r="M7" s="71" t="inlineStr">
         <is>
           <t>비파괴 검사</t>
         </is>
       </c>
-      <c r="N7" s="203" t="n"/>
-      <c r="O7" s="203" t="n"/>
-      <c r="P7" s="201" t="n"/>
-      <c r="Q7" s="205" t="inlineStr">
+      <c r="N7" s="45" t="n"/>
+      <c r="O7" s="45" t="n"/>
+      <c r="P7" s="46" t="n"/>
+      <c r="Q7" s="33" t="inlineStr">
         <is>
           <t>방사선투과검사(RT)</t>
         </is>
       </c>
-      <c r="R7" s="192" t="n"/>
-      <c r="S7" s="192" t="n"/>
-      <c r="T7" s="192" t="n"/>
-      <c r="U7" s="192" t="n"/>
-      <c r="V7" s="192" t="n"/>
-      <c r="W7" s="198" t="n"/>
-      <c r="X7" s="205" t="inlineStr">
+      <c r="R7" s="59" t="n"/>
+      <c r="S7" s="59" t="n"/>
+      <c r="T7" s="59" t="n"/>
+      <c r="U7" s="59" t="n"/>
+      <c r="V7" s="59" t="n"/>
+      <c r="W7" s="60" t="n"/>
+      <c r="X7" s="33" t="inlineStr">
         <is>
           <t>UT</t>
         </is>
       </c>
-      <c r="Y7" s="205" t="inlineStr">
+      <c r="Y7" s="33" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="Z7" s="215" t="inlineStr">
+      <c r="Z7" s="85" t="inlineStr">
         <is>
           <t>이물질검사</t>
         </is>
       </c>
-      <c r="AA7" s="216" t="inlineStr">
+      <c r="AA7" s="91" t="inlineStr">
         <is>
           <t>비괴사역행서</t>
         </is>
       </c>
-      <c r="AB7" s="217" t="inlineStr">
+      <c r="AB7" s="63" t="inlineStr">
         <is>
           <t>파검용수자명</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="12" customFormat="1" customHeight="1" s="4">
-      <c r="A8" s="189" t="n"/>
-      <c r="B8" s="191" t="n"/>
-      <c r="C8" s="208" t="n"/>
-      <c r="D8" s="191" t="n"/>
-      <c r="E8" s="208" t="n"/>
-      <c r="F8" s="191" t="n"/>
-      <c r="G8" s="208" t="n"/>
-      <c r="H8" s="190" t="n"/>
-      <c r="I8" s="190" t="n"/>
-      <c r="J8" s="190" t="n"/>
-      <c r="K8" s="191" t="n"/>
-      <c r="L8" s="103" t="inlineStr">
+    <row r="8" ht="12" customFormat="1" customHeight="1" s="44">
+      <c r="A8" s="57" t="n"/>
+      <c r="B8" s="50" t="n"/>
+      <c r="C8" s="48" t="n"/>
+      <c r="D8" s="50" t="n"/>
+      <c r="E8" s="48" t="n"/>
+      <c r="F8" s="50" t="n"/>
+      <c r="G8" s="48" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="50" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="M8" s="104" t="inlineStr">
+      <c r="M8" s="52" t="inlineStr">
         <is>
           <t>요 청 항 목</t>
         </is>
       </c>
-      <c r="N8" s="190" t="n"/>
-      <c r="O8" s="190" t="n"/>
-      <c r="P8" s="191" t="n"/>
-      <c r="Q8" s="205" t="inlineStr">
+      <c r="N8" s="49" t="n"/>
+      <c r="O8" s="49" t="n"/>
+      <c r="P8" s="50" t="n"/>
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t>④필름 번호</t>
         </is>
       </c>
-      <c r="R8" s="192" t="n"/>
-      <c r="S8" s="192" t="n"/>
-      <c r="T8" s="192" t="n"/>
-      <c r="U8" s="192" t="n"/>
-      <c r="V8" s="192" t="n"/>
-      <c r="W8" s="198" t="n"/>
-      <c r="X8" s="218" t="n"/>
-      <c r="Y8" s="218" t="n"/>
-      <c r="Z8" s="218" t="n"/>
-      <c r="AA8" s="209" t="n"/>
-      <c r="AB8" s="219" t="n"/>
+      <c r="R8" s="59" t="n"/>
+      <c r="S8" s="59" t="n"/>
+      <c r="T8" s="59" t="n"/>
+      <c r="U8" s="59" t="n"/>
+      <c r="V8" s="59" t="n"/>
+      <c r="W8" s="60" t="n"/>
+      <c r="X8" s="34" t="n"/>
+      <c r="Y8" s="34" t="n"/>
+      <c r="Z8" s="34" t="n"/>
+      <c r="AA8" s="47" t="n"/>
+      <c r="AB8" s="64" t="n"/>
     </row>
-    <row r="9" ht="12" customFormat="1" customHeight="1" s="4">
-      <c r="A9" s="220" t="inlineStr">
+    <row r="9" ht="12" customFormat="1" customHeight="1" s="44">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="B9" s="205" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>용접부</t>
         </is>
       </c>
-      <c r="C9" s="221" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>파이프
 번  호
 (---&gt;)</t>
         </is>
       </c>
-      <c r="D9" s="221" t="inlineStr">
+      <c r="D9" s="51" t="inlineStr">
         <is>
           <t>용접사
 번  호</t>
         </is>
       </c>
-      <c r="E9" s="221" t="inlineStr">
+      <c r="E9" s="51" t="inlineStr">
         <is>
           <t>파이프
 구 경
 및 두께</t>
         </is>
       </c>
-      <c r="F9" s="221" t="inlineStr">
+      <c r="F9" s="51" t="inlineStr">
         <is>
           <t>파이프
 재  질</t>
         </is>
       </c>
-      <c r="G9" s="221" t="inlineStr">
+      <c r="G9" s="51" t="inlineStr">
         <is>
           <t>①O
 R
@@ -2813,14 +2368,14 @@
 A</t>
         </is>
       </c>
-      <c r="H9" s="221" t="inlineStr">
+      <c r="H9" s="51" t="inlineStr">
         <is>
           <t>FIT
 -
 UP</t>
         </is>
       </c>
-      <c r="I9" s="221" t="inlineStr">
+      <c r="I9" s="51" t="inlineStr">
         <is>
           <t>예열 
 및
@@ -2828,20 +2383,20 @@
 검사</t>
         </is>
       </c>
-      <c r="J9" s="221" t="inlineStr">
+      <c r="J9" s="51" t="inlineStr">
         <is>
           <t>청결
 상태</t>
         </is>
       </c>
-      <c r="K9" s="221" t="inlineStr">
+      <c r="K9" s="51" t="inlineStr">
         <is>
           <t>현장
 안전
 상태</t>
         </is>
       </c>
-      <c r="L9" s="107" t="inlineStr">
+      <c r="L9" s="92" t="inlineStr">
         <is>
           <t>시공
 감독
@@ -2849,180 +2404,180 @@
 (R/W)</t>
         </is>
       </c>
-      <c r="M9" s="205" t="inlineStr">
+      <c r="M9" s="33" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
       </c>
-      <c r="N9" s="205" t="inlineStr">
+      <c r="N9" s="33" t="inlineStr">
         <is>
           <t>UT</t>
         </is>
       </c>
-      <c r="O9" s="205" t="inlineStr">
+      <c r="O9" s="33" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="P9" s="221" t="inlineStr">
+      <c r="P9" s="51" t="inlineStr">
         <is>
           <t>이물
 질
 검사</t>
         </is>
       </c>
-      <c r="Q9" s="205" t="n">
+      <c r="Q9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="205" t="n">
+      <c r="R9" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="S9" s="205" t="n">
+      <c r="S9" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="T9" s="205" t="n">
+      <c r="T9" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="U9" s="205" t="n">
+      <c r="U9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="205" t="n">
+      <c r="V9" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="W9" s="205" t="n">
+      <c r="W9" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="X9" s="218" t="n"/>
-      <c r="Y9" s="218" t="n"/>
-      <c r="Z9" s="218" t="n"/>
-      <c r="AA9" s="209" t="n"/>
-      <c r="AB9" s="219" t="n"/>
+      <c r="X9" s="34" t="n"/>
+      <c r="Y9" s="34" t="n"/>
+      <c r="Z9" s="34" t="n"/>
+      <c r="AA9" s="47" t="n"/>
+      <c r="AB9" s="64" t="n"/>
     </row>
-    <row r="10" ht="12" customFormat="1" customHeight="1" s="4">
-      <c r="A10" s="222" t="n"/>
-      <c r="B10" s="218" t="n"/>
-      <c r="C10" s="218" t="n"/>
-      <c r="D10" s="218" t="n"/>
-      <c r="E10" s="218" t="n"/>
-      <c r="F10" s="218" t="n"/>
-      <c r="G10" s="218" t="n"/>
-      <c r="H10" s="218" t="n"/>
-      <c r="I10" s="218" t="n"/>
-      <c r="J10" s="218" t="n"/>
-      <c r="K10" s="218" t="n"/>
-      <c r="L10" s="218" t="n"/>
-      <c r="M10" s="218" t="n"/>
-      <c r="N10" s="218" t="n"/>
-      <c r="O10" s="218" t="n"/>
-      <c r="P10" s="218" t="n"/>
-      <c r="Q10" s="218" t="n"/>
-      <c r="R10" s="218" t="n"/>
-      <c r="S10" s="218" t="n"/>
-      <c r="T10" s="218" t="n"/>
-      <c r="U10" s="218" t="n"/>
-      <c r="V10" s="218" t="n"/>
-      <c r="W10" s="218" t="n"/>
-      <c r="X10" s="218" t="n"/>
-      <c r="Y10" s="218" t="n"/>
-      <c r="Z10" s="218" t="n"/>
-      <c r="AA10" s="209" t="n"/>
-      <c r="AB10" s="219" t="n"/>
+    <row r="10" ht="12" customFormat="1" customHeight="1" s="44">
+      <c r="A10" s="82" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="34" t="n"/>
+      <c r="H10" s="34" t="n"/>
+      <c r="I10" s="34" t="n"/>
+      <c r="J10" s="34" t="n"/>
+      <c r="K10" s="34" t="n"/>
+      <c r="L10" s="34" t="n"/>
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="34" t="n"/>
+      <c r="O10" s="34" t="n"/>
+      <c r="P10" s="34" t="n"/>
+      <c r="Q10" s="34" t="n"/>
+      <c r="R10" s="34" t="n"/>
+      <c r="S10" s="34" t="n"/>
+      <c r="T10" s="34" t="n"/>
+      <c r="U10" s="34" t="n"/>
+      <c r="V10" s="34" t="n"/>
+      <c r="W10" s="34" t="n"/>
+      <c r="X10" s="34" t="n"/>
+      <c r="Y10" s="34" t="n"/>
+      <c r="Z10" s="34" t="n"/>
+      <c r="AA10" s="47" t="n"/>
+      <c r="AB10" s="64" t="n"/>
     </row>
-    <row r="11" ht="12" customFormat="1" customHeight="1" s="4">
-      <c r="A11" s="222" t="n"/>
-      <c r="B11" s="218" t="n"/>
-      <c r="C11" s="218" t="n"/>
-      <c r="D11" s="218" t="n"/>
-      <c r="E11" s="218" t="n"/>
-      <c r="F11" s="218" t="n"/>
-      <c r="G11" s="218" t="n"/>
-      <c r="H11" s="218" t="n"/>
-      <c r="I11" s="218" t="n"/>
-      <c r="J11" s="218" t="n"/>
-      <c r="K11" s="218" t="n"/>
-      <c r="L11" s="218" t="n"/>
-      <c r="M11" s="218" t="n"/>
-      <c r="N11" s="218" t="n"/>
-      <c r="O11" s="218" t="n"/>
-      <c r="P11" s="218" t="n"/>
-      <c r="Q11" s="218" t="n"/>
-      <c r="R11" s="218" t="n"/>
-      <c r="S11" s="218" t="n"/>
-      <c r="T11" s="218" t="n"/>
-      <c r="U11" s="218" t="n"/>
-      <c r="V11" s="218" t="n"/>
-      <c r="W11" s="218" t="n"/>
-      <c r="X11" s="218" t="n"/>
-      <c r="Y11" s="218" t="n"/>
-      <c r="Z11" s="218" t="n"/>
-      <c r="AA11" s="209" t="n"/>
-      <c r="AB11" s="219" t="n"/>
+    <row r="11" ht="12" customFormat="1" customHeight="1" s="44">
+      <c r="A11" s="82" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="34" t="n"/>
+      <c r="O11" s="34" t="n"/>
+      <c r="P11" s="34" t="n"/>
+      <c r="Q11" s="34" t="n"/>
+      <c r="R11" s="34" t="n"/>
+      <c r="S11" s="34" t="n"/>
+      <c r="T11" s="34" t="n"/>
+      <c r="U11" s="34" t="n"/>
+      <c r="V11" s="34" t="n"/>
+      <c r="W11" s="34" t="n"/>
+      <c r="X11" s="34" t="n"/>
+      <c r="Y11" s="34" t="n"/>
+      <c r="Z11" s="34" t="n"/>
+      <c r="AA11" s="47" t="n"/>
+      <c r="AB11" s="64" t="n"/>
     </row>
-    <row r="12" ht="12" customFormat="1" customHeight="1" s="4">
-      <c r="A12" s="222" t="n"/>
-      <c r="B12" s="218" t="n"/>
-      <c r="C12" s="218" t="n"/>
-      <c r="D12" s="218" t="n"/>
-      <c r="E12" s="218" t="n"/>
-      <c r="F12" s="218" t="n"/>
-      <c r="G12" s="218" t="n"/>
-      <c r="H12" s="218" t="n"/>
-      <c r="I12" s="218" t="n"/>
-      <c r="J12" s="218" t="n"/>
-      <c r="K12" s="218" t="n"/>
-      <c r="L12" s="218" t="n"/>
-      <c r="M12" s="218" t="n"/>
-      <c r="N12" s="218" t="n"/>
-      <c r="O12" s="218" t="n"/>
-      <c r="P12" s="218" t="n"/>
-      <c r="Q12" s="218" t="n"/>
-      <c r="R12" s="218" t="n"/>
-      <c r="S12" s="218" t="n"/>
-      <c r="T12" s="218" t="n"/>
-      <c r="U12" s="218" t="n"/>
-      <c r="V12" s="218" t="n"/>
-      <c r="W12" s="218" t="n"/>
-      <c r="X12" s="218" t="n"/>
-      <c r="Y12" s="218" t="n"/>
-      <c r="Z12" s="218" t="n"/>
-      <c r="AA12" s="209" t="n"/>
-      <c r="AB12" s="219" t="n"/>
+    <row r="12" ht="12" customFormat="1" customHeight="1" s="44">
+      <c r="A12" s="82" t="n"/>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="34" t="n"/>
+      <c r="I12" s="34" t="n"/>
+      <c r="J12" s="34" t="n"/>
+      <c r="K12" s="34" t="n"/>
+      <c r="L12" s="34" t="n"/>
+      <c r="M12" s="34" t="n"/>
+      <c r="N12" s="34" t="n"/>
+      <c r="O12" s="34" t="n"/>
+      <c r="P12" s="34" t="n"/>
+      <c r="Q12" s="34" t="n"/>
+      <c r="R12" s="34" t="n"/>
+      <c r="S12" s="34" t="n"/>
+      <c r="T12" s="34" t="n"/>
+      <c r="U12" s="34" t="n"/>
+      <c r="V12" s="34" t="n"/>
+      <c r="W12" s="34" t="n"/>
+      <c r="X12" s="34" t="n"/>
+      <c r="Y12" s="34" t="n"/>
+      <c r="Z12" s="34" t="n"/>
+      <c r="AA12" s="47" t="n"/>
+      <c r="AB12" s="64" t="n"/>
     </row>
-    <row r="13" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A13" s="223" t="n"/>
-      <c r="B13" s="224" t="n"/>
-      <c r="C13" s="224" t="n"/>
-      <c r="D13" s="224" t="n"/>
-      <c r="E13" s="224" t="n"/>
-      <c r="F13" s="224" t="n"/>
-      <c r="G13" s="224" t="n"/>
-      <c r="H13" s="224" t="n"/>
-      <c r="I13" s="224" t="n"/>
-      <c r="J13" s="224" t="n"/>
-      <c r="K13" s="224" t="n"/>
-      <c r="L13" s="224" t="n"/>
-      <c r="M13" s="224" t="n"/>
-      <c r="N13" s="224" t="n"/>
-      <c r="O13" s="224" t="n"/>
-      <c r="P13" s="224" t="n"/>
-      <c r="Q13" s="224" t="n"/>
-      <c r="R13" s="224" t="n"/>
-      <c r="S13" s="224" t="n"/>
-      <c r="T13" s="224" t="n"/>
-      <c r="U13" s="224" t="n"/>
-      <c r="V13" s="224" t="n"/>
-      <c r="W13" s="224" t="n"/>
-      <c r="X13" s="224" t="n"/>
-      <c r="Y13" s="224" t="n"/>
-      <c r="Z13" s="224" t="n"/>
-      <c r="AA13" s="208" t="n"/>
-      <c r="AB13" s="211" t="n"/>
+    <row r="13" ht="18" customFormat="1" customHeight="1" s="44">
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="31" t="n"/>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="31" t="n"/>
+      <c r="K13" s="31" t="n"/>
+      <c r="L13" s="31" t="n"/>
+      <c r="M13" s="31" t="n"/>
+      <c r="N13" s="31" t="n"/>
+      <c r="O13" s="31" t="n"/>
+      <c r="P13" s="31" t="n"/>
+      <c r="Q13" s="31" t="n"/>
+      <c r="R13" s="31" t="n"/>
+      <c r="S13" s="31" t="n"/>
+      <c r="T13" s="31" t="n"/>
+      <c r="U13" s="31" t="n"/>
+      <c r="V13" s="31" t="n"/>
+      <c r="W13" s="31" t="n"/>
+      <c r="X13" s="31" t="n"/>
+      <c r="Y13" s="31" t="n"/>
+      <c r="Z13" s="31" t="n"/>
+      <c r="AA13" s="48" t="n"/>
+      <c r="AB13" s="55" t="n"/>
     </row>
-    <row r="14" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A14" s="225" t="n">
+    <row r="14" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="226" t="n">
+      <c r="B14" s="108" t="n">
         <v>63</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3045,76 +2600,96 @@
           <t xml:space="preserve">API 5L </t>
         </is>
       </c>
-      <c r="G14" s="227" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H14" s="228" t="inlineStr">
+      <c r="H14" s="35" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I14" s="228" t="inlineStr">
+      <c r="I14" s="35" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="J14" s="227" t="inlineStr">
+      <c r="J14" s="30" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="K14" s="227" t="inlineStr">
+      <c r="K14" s="30" t="inlineStr">
         <is>
           <t>Test1, Test2</t>
         </is>
       </c>
-      <c r="L14" s="229" t="n"/>
-      <c r="M14" s="227" t="inlineStr">
+      <c r="L14" s="42" t="n"/>
+      <c r="M14" s="30" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="227" t="n"/>
-      <c r="O14" s="227" t="inlineStr">
+      <c r="N14" s="30" t="n"/>
+      <c r="O14" s="30" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="P14" s="230" t="inlineStr">
+      <c r="P14" s="109" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="Q14" s="227" t="inlineStr">
+      <c r="Q14" s="30" t="inlineStr">
         <is>
           <t>1/P</t>
         </is>
       </c>
-      <c r="R14" s="227" t="inlineStr">
+      <c r="R14" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S14" s="227" t="n"/>
-      <c r="T14" s="227" t="n"/>
-      <c r="U14" s="227" t="n"/>
-      <c r="V14" s="227" t="n"/>
-      <c r="W14" s="227" t="n"/>
-      <c r="X14" s="227" t="n"/>
-      <c r="Y14" s="227" t="inlineStr">
+      <c r="S14" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T14" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U14" s="30" t="inlineStr">
         <is>
           <t>1/P</t>
         </is>
       </c>
-      <c r="Z14" s="227" t="n"/>
-      <c r="AA14" s="231" t="n"/>
-      <c r="AB14" s="207" t="n"/>
+      <c r="V14" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" s="30" t="inlineStr">
+        <is>
+          <t>1/P</t>
+        </is>
+      </c>
+      <c r="X14" s="30" t="n"/>
+      <c r="Y14" s="30" t="inlineStr">
+        <is>
+          <t>1/P</t>
+        </is>
+      </c>
+      <c r="Z14" s="30" t="n"/>
+      <c r="AA14" s="73" t="n"/>
+      <c r="AB14" s="54" t="n"/>
     </row>
-    <row r="15" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A15" s="223" t="n"/>
-      <c r="B15" s="224" t="n"/>
+    <row r="15" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="31" t="n"/>
       <c r="C15" s="12" t="inlineStr">
         <is>
           <t>HS2025-04-095</t>
@@ -3135,42 +2710,42 @@
           <t>GR.X70</t>
         </is>
       </c>
-      <c r="G15" s="224" t="n"/>
-      <c r="H15" s="224" t="n"/>
-      <c r="I15" s="224" t="n"/>
-      <c r="J15" s="224" t="n"/>
-      <c r="K15" s="224" t="n"/>
-      <c r="L15" s="224" t="n"/>
-      <c r="M15" s="224" t="n"/>
-      <c r="N15" s="224" t="n"/>
-      <c r="O15" s="224" t="n"/>
-      <c r="P15" s="224" t="n"/>
-      <c r="Q15" s="224" t="n"/>
-      <c r="R15" s="224" t="n"/>
-      <c r="S15" s="224" t="n"/>
-      <c r="T15" s="224" t="n"/>
-      <c r="U15" s="224" t="n"/>
-      <c r="V15" s="224" t="n"/>
-      <c r="W15" s="224" t="n"/>
-      <c r="X15" s="224" t="n"/>
-      <c r="Y15" s="224" t="n"/>
-      <c r="Z15" s="224" t="n"/>
-      <c r="AA15" s="208" t="n"/>
-      <c r="AB15" s="211" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="31" t="n"/>
+      <c r="I15" s="31" t="n"/>
+      <c r="J15" s="31" t="n"/>
+      <c r="K15" s="31" t="n"/>
+      <c r="L15" s="31" t="n"/>
+      <c r="M15" s="31" t="n"/>
+      <c r="N15" s="31" t="n"/>
+      <c r="O15" s="31" t="n"/>
+      <c r="P15" s="31" t="n"/>
+      <c r="Q15" s="31" t="n"/>
+      <c r="R15" s="31" t="n"/>
+      <c r="S15" s="31" t="n"/>
+      <c r="T15" s="31" t="n"/>
+      <c r="U15" s="31" t="n"/>
+      <c r="V15" s="31" t="n"/>
+      <c r="W15" s="31" t="n"/>
+      <c r="X15" s="31" t="n"/>
+      <c r="Y15" s="31" t="n"/>
+      <c r="Z15" s="31" t="n"/>
+      <c r="AA15" s="48" t="n"/>
+      <c r="AB15" s="55" t="n"/>
       <c r="AF15" s="18" t="n"/>
       <c r="AH15" s="19" t="n"/>
-      <c r="AI15" s="94" t="n"/>
-      <c r="AK15" s="94" t="n"/>
+      <c r="AI15" s="40" t="n"/>
+      <c r="AK15" s="40" t="n"/>
       <c r="AL15" s="19" t="n"/>
-      <c r="AM15" s="94" t="n"/>
-      <c r="AN15" s="94" t="n"/>
+      <c r="AM15" s="40" t="n"/>
+      <c r="AN15" s="40" t="n"/>
       <c r="AO15" s="21" t="n"/>
     </row>
-    <row r="16" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A16" s="225" t="n">
+    <row r="16" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A16" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="226" t="n">
+      <c r="B16" s="108" t="n">
         <v>64</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -3193,60 +2768,88 @@
           <t xml:space="preserve">API 5L </t>
         </is>
       </c>
-      <c r="G16" s="227" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H16" s="228" t="inlineStr">
+      <c r="H16" s="35" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I16" s="228" t="inlineStr">
+      <c r="I16" s="35" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="J16" s="227" t="inlineStr">
+      <c r="J16" s="30" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="K16" s="227" t="inlineStr">
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="L16" s="229" t="n"/>
-      <c r="M16" s="227" t="inlineStr">
+      <c r="L16" s="42" t="n"/>
+      <c r="M16" s="30" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="227" t="n"/>
-      <c r="O16" s="227" t="n"/>
-      <c r="P16" s="230" t="inlineStr">
+      <c r="N16" s="30" t="n"/>
+      <c r="O16" s="30" t="n"/>
+      <c r="P16" s="109" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="Q16" s="227" t="n"/>
-      <c r="R16" s="227" t="n"/>
-      <c r="S16" s="227" t="n"/>
-      <c r="T16" s="227" t="n"/>
-      <c r="U16" s="227" t="n"/>
-      <c r="V16" s="227" t="n"/>
-      <c r="W16" s="227" t="n"/>
-      <c r="X16" s="227" t="n"/>
-      <c r="Y16" s="227" t="n"/>
-      <c r="Z16" s="227" t="n"/>
-      <c r="AA16" s="231" t="n"/>
-      <c r="AB16" s="207" t="n"/>
+      <c r="Q16" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S16" s="30" t="inlineStr">
+        <is>
+          <t>1/P</t>
+        </is>
+      </c>
+      <c r="T16" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U16" s="30" t="inlineStr">
+        <is>
+          <t>1/P</t>
+        </is>
+      </c>
+      <c r="V16" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X16" s="30" t="n"/>
+      <c r="Y16" s="30" t="n"/>
+      <c r="Z16" s="30" t="n"/>
+      <c r="AA16" s="73" t="n"/>
+      <c r="AB16" s="54" t="n"/>
     </row>
-    <row r="17" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A17" s="223" t="n"/>
-      <c r="B17" s="224" t="n"/>
+    <row r="17" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="31" t="n"/>
       <c r="C17" s="22" t="inlineStr">
         <is>
           <t>HS2025-04-160</t>
@@ -3267,458 +2870,458 @@
           <t>GR.X70</t>
         </is>
       </c>
-      <c r="G17" s="224" t="n"/>
-      <c r="H17" s="224" t="n"/>
-      <c r="I17" s="224" t="n"/>
-      <c r="J17" s="224" t="n"/>
-      <c r="K17" s="224" t="n"/>
-      <c r="L17" s="224" t="n"/>
-      <c r="M17" s="224" t="n"/>
-      <c r="N17" s="224" t="n"/>
-      <c r="O17" s="224" t="n"/>
-      <c r="P17" s="224" t="n"/>
-      <c r="Q17" s="224" t="n"/>
-      <c r="R17" s="224" t="n"/>
-      <c r="S17" s="224" t="n"/>
-      <c r="T17" s="224" t="n"/>
-      <c r="U17" s="224" t="n"/>
-      <c r="V17" s="224" t="n"/>
-      <c r="W17" s="224" t="n"/>
-      <c r="X17" s="224" t="n"/>
-      <c r="Y17" s="224" t="n"/>
-      <c r="Z17" s="224" t="n"/>
-      <c r="AA17" s="208" t="n"/>
-      <c r="AB17" s="211" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="31" t="n"/>
+      <c r="I17" s="31" t="n"/>
+      <c r="J17" s="31" t="n"/>
+      <c r="K17" s="31" t="n"/>
+      <c r="L17" s="31" t="n"/>
+      <c r="M17" s="31" t="n"/>
+      <c r="N17" s="31" t="n"/>
+      <c r="O17" s="31" t="n"/>
+      <c r="P17" s="31" t="n"/>
+      <c r="Q17" s="31" t="n"/>
+      <c r="R17" s="31" t="n"/>
+      <c r="S17" s="31" t="n"/>
+      <c r="T17" s="31" t="n"/>
+      <c r="U17" s="31" t="n"/>
+      <c r="V17" s="31" t="n"/>
+      <c r="W17" s="31" t="n"/>
+      <c r="X17" s="31" t="n"/>
+      <c r="Y17" s="31" t="n"/>
+      <c r="Z17" s="31" t="n"/>
+      <c r="AA17" s="48" t="n"/>
+      <c r="AB17" s="55" t="n"/>
       <c r="AF17" s="18" t="n"/>
-      <c r="AG17" s="99" t="n"/>
+      <c r="AG17" s="43" t="n"/>
       <c r="AH17" s="19" t="n"/>
-      <c r="AI17" s="94" t="n"/>
-      <c r="AJ17" s="94" t="n"/>
-      <c r="AK17" s="94" t="n"/>
+      <c r="AI17" s="40" t="n"/>
+      <c r="AJ17" s="40" t="n"/>
+      <c r="AK17" s="40" t="n"/>
       <c r="AL17" s="19" t="n"/>
-      <c r="AM17" s="94" t="n"/>
-      <c r="AN17" s="94" t="n"/>
+      <c r="AM17" s="40" t="n"/>
+      <c r="AN17" s="40" t="n"/>
       <c r="AO17" s="21" t="n"/>
-      <c r="AP17" s="94" t="n"/>
+      <c r="AP17" s="40" t="n"/>
     </row>
-    <row r="18" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A18" s="225" t="n"/>
-      <c r="B18" s="232" t="n"/>
+    <row r="18" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="110" t="n"/>
       <c r="C18" s="12" t="n"/>
       <c r="D18" s="13" t="n"/>
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="227" t="n"/>
-      <c r="H18" s="228" t="n"/>
-      <c r="I18" s="228" t="n"/>
-      <c r="J18" s="227" t="n"/>
-      <c r="K18" s="227" t="n"/>
-      <c r="L18" s="229" t="n"/>
-      <c r="M18" s="227" t="n"/>
-      <c r="N18" s="227" t="n"/>
-      <c r="O18" s="227" t="n"/>
-      <c r="P18" s="230" t="n"/>
-      <c r="Q18" s="227" t="n"/>
-      <c r="R18" s="227" t="n"/>
-      <c r="S18" s="227" t="n"/>
-      <c r="T18" s="227" t="n"/>
-      <c r="U18" s="227" t="n"/>
-      <c r="V18" s="227" t="n"/>
-      <c r="W18" s="227" t="n"/>
-      <c r="X18" s="227" t="n"/>
-      <c r="Y18" s="227" t="n"/>
-      <c r="Z18" s="227" t="n"/>
-      <c r="AA18" s="231" t="n"/>
-      <c r="AB18" s="207" t="n"/>
+      <c r="G18" s="30" t="n"/>
+      <c r="H18" s="35" t="n"/>
+      <c r="I18" s="35" t="n"/>
+      <c r="J18" s="30" t="n"/>
+      <c r="K18" s="30" t="n"/>
+      <c r="L18" s="42" t="n"/>
+      <c r="M18" s="30" t="n"/>
+      <c r="N18" s="30" t="n"/>
+      <c r="O18" s="30" t="n"/>
+      <c r="P18" s="109" t="n"/>
+      <c r="Q18" s="30" t="n"/>
+      <c r="R18" s="30" t="n"/>
+      <c r="S18" s="30" t="n"/>
+      <c r="T18" s="30" t="n"/>
+      <c r="U18" s="30" t="n"/>
+      <c r="V18" s="30" t="n"/>
+      <c r="W18" s="30" t="n"/>
+      <c r="X18" s="30" t="n"/>
+      <c r="Y18" s="30" t="n"/>
+      <c r="Z18" s="30" t="n"/>
+      <c r="AA18" s="73" t="n"/>
+      <c r="AB18" s="54" t="n"/>
       <c r="AF18" s="18" t="n"/>
       <c r="AH18" s="19" t="n"/>
-      <c r="AI18" s="94" t="n"/>
-      <c r="AK18" s="94" t="n"/>
-      <c r="AL18" s="94" t="n"/>
-      <c r="AM18" s="94" t="n"/>
-      <c r="AN18" s="94" t="n"/>
+      <c r="AI18" s="40" t="n"/>
+      <c r="AK18" s="40" t="n"/>
+      <c r="AL18" s="40" t="n"/>
+      <c r="AM18" s="40" t="n"/>
+      <c r="AN18" s="40" t="n"/>
       <c r="AO18" s="21" t="n"/>
     </row>
-    <row r="19" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A19" s="223" t="n"/>
-      <c r="B19" s="224" t="n"/>
+    <row r="19" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="31" t="n"/>
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="16" t="n"/>
       <c r="E19" s="14" t="n"/>
       <c r="F19" s="17" t="n"/>
-      <c r="G19" s="224" t="n"/>
-      <c r="H19" s="224" t="n"/>
-      <c r="I19" s="224" t="n"/>
-      <c r="J19" s="224" t="n"/>
-      <c r="K19" s="224" t="n"/>
-      <c r="L19" s="224" t="n"/>
-      <c r="M19" s="224" t="n"/>
-      <c r="N19" s="224" t="n"/>
-      <c r="O19" s="224" t="n"/>
-      <c r="P19" s="224" t="n"/>
-      <c r="Q19" s="224" t="n"/>
-      <c r="R19" s="224" t="n"/>
-      <c r="S19" s="224" t="n"/>
-      <c r="T19" s="224" t="n"/>
-      <c r="U19" s="224" t="n"/>
-      <c r="V19" s="224" t="n"/>
-      <c r="W19" s="224" t="n"/>
-      <c r="X19" s="224" t="n"/>
-      <c r="Y19" s="224" t="n"/>
-      <c r="Z19" s="224" t="n"/>
-      <c r="AA19" s="208" t="n"/>
-      <c r="AB19" s="211" t="n"/>
+      <c r="G19" s="31" t="n"/>
+      <c r="H19" s="31" t="n"/>
+      <c r="I19" s="31" t="n"/>
+      <c r="J19" s="31" t="n"/>
+      <c r="K19" s="31" t="n"/>
+      <c r="L19" s="31" t="n"/>
+      <c r="M19" s="31" t="n"/>
+      <c r="N19" s="31" t="n"/>
+      <c r="O19" s="31" t="n"/>
+      <c r="P19" s="31" t="n"/>
+      <c r="Q19" s="31" t="n"/>
+      <c r="R19" s="31" t="n"/>
+      <c r="S19" s="31" t="n"/>
+      <c r="T19" s="31" t="n"/>
+      <c r="U19" s="31" t="n"/>
+      <c r="V19" s="31" t="n"/>
+      <c r="W19" s="31" t="n"/>
+      <c r="X19" s="31" t="n"/>
+      <c r="Y19" s="31" t="n"/>
+      <c r="Z19" s="31" t="n"/>
+      <c r="AA19" s="48" t="n"/>
+      <c r="AB19" s="55" t="n"/>
     </row>
-    <row r="20" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A20" s="225" t="n"/>
-      <c r="B20" s="233" t="n"/>
+    <row r="20" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="84" t="n"/>
       <c r="C20" s="22" t="n"/>
       <c r="D20" s="13" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="227" t="n"/>
-      <c r="H20" s="227" t="n"/>
-      <c r="I20" s="227" t="n"/>
-      <c r="J20" s="227" t="n"/>
-      <c r="K20" s="227" t="n"/>
-      <c r="L20" s="229" t="n"/>
-      <c r="M20" s="227" t="n"/>
-      <c r="N20" s="227" t="n"/>
-      <c r="O20" s="227" t="n"/>
-      <c r="P20" s="230" t="n"/>
-      <c r="Q20" s="227" t="n"/>
-      <c r="R20" s="227" t="n"/>
-      <c r="S20" s="227" t="n"/>
-      <c r="T20" s="227" t="n"/>
-      <c r="U20" s="227" t="n"/>
-      <c r="V20" s="227" t="n"/>
-      <c r="W20" s="227" t="n"/>
-      <c r="X20" s="227" t="n"/>
-      <c r="Y20" s="227" t="n"/>
-      <c r="Z20" s="227" t="n"/>
-      <c r="AA20" s="231" t="n"/>
-      <c r="AB20" s="207" t="n"/>
+      <c r="G20" s="30" t="n"/>
+      <c r="H20" s="30" t="n"/>
+      <c r="I20" s="30" t="n"/>
+      <c r="J20" s="30" t="n"/>
+      <c r="K20" s="30" t="n"/>
+      <c r="L20" s="42" t="n"/>
+      <c r="M20" s="30" t="n"/>
+      <c r="N20" s="30" t="n"/>
+      <c r="O20" s="30" t="n"/>
+      <c r="P20" s="109" t="n"/>
+      <c r="Q20" s="30" t="n"/>
+      <c r="R20" s="30" t="n"/>
+      <c r="S20" s="30" t="n"/>
+      <c r="T20" s="30" t="n"/>
+      <c r="U20" s="30" t="n"/>
+      <c r="V20" s="30" t="n"/>
+      <c r="W20" s="30" t="n"/>
+      <c r="X20" s="30" t="n"/>
+      <c r="Y20" s="30" t="n"/>
+      <c r="Z20" s="30" t="n"/>
+      <c r="AA20" s="73" t="n"/>
+      <c r="AB20" s="54" t="n"/>
     </row>
-    <row r="21" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A21" s="223" t="n"/>
-      <c r="B21" s="224" t="n"/>
+    <row r="21" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A21" s="37" t="n"/>
+      <c r="B21" s="31" t="n"/>
       <c r="C21" s="22" t="n"/>
       <c r="D21" s="16" t="n"/>
       <c r="E21" s="14" t="n"/>
       <c r="F21" s="17" t="n"/>
-      <c r="G21" s="224" t="n"/>
-      <c r="H21" s="224" t="n"/>
-      <c r="I21" s="224" t="n"/>
-      <c r="J21" s="224" t="n"/>
-      <c r="K21" s="224" t="n"/>
-      <c r="L21" s="224" t="n"/>
-      <c r="M21" s="224" t="n"/>
-      <c r="N21" s="224" t="n"/>
-      <c r="O21" s="224" t="n"/>
-      <c r="P21" s="224" t="n"/>
-      <c r="Q21" s="224" t="n"/>
-      <c r="R21" s="224" t="n"/>
-      <c r="S21" s="224" t="n"/>
-      <c r="T21" s="224" t="n"/>
-      <c r="U21" s="224" t="n"/>
-      <c r="V21" s="224" t="n"/>
-      <c r="W21" s="224" t="n"/>
-      <c r="X21" s="224" t="n"/>
-      <c r="Y21" s="224" t="n"/>
-      <c r="Z21" s="224" t="n"/>
-      <c r="AA21" s="208" t="n"/>
-      <c r="AB21" s="211" t="n"/>
+      <c r="G21" s="31" t="n"/>
+      <c r="H21" s="31" t="n"/>
+      <c r="I21" s="31" t="n"/>
+      <c r="J21" s="31" t="n"/>
+      <c r="K21" s="31" t="n"/>
+      <c r="L21" s="31" t="n"/>
+      <c r="M21" s="31" t="n"/>
+      <c r="N21" s="31" t="n"/>
+      <c r="O21" s="31" t="n"/>
+      <c r="P21" s="31" t="n"/>
+      <c r="Q21" s="31" t="n"/>
+      <c r="R21" s="31" t="n"/>
+      <c r="S21" s="31" t="n"/>
+      <c r="T21" s="31" t="n"/>
+      <c r="U21" s="31" t="n"/>
+      <c r="V21" s="31" t="n"/>
+      <c r="W21" s="31" t="n"/>
+      <c r="X21" s="31" t="n"/>
+      <c r="Y21" s="31" t="n"/>
+      <c r="Z21" s="31" t="n"/>
+      <c r="AA21" s="48" t="n"/>
+      <c r="AB21" s="55" t="n"/>
     </row>
-    <row r="22" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A22" s="225" t="n"/>
-      <c r="B22" s="233" t="n"/>
+    <row r="22" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="84" t="n"/>
       <c r="C22" s="22" t="n"/>
       <c r="D22" s="13" t="n"/>
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="227" t="n"/>
-      <c r="H22" s="227" t="n"/>
-      <c r="I22" s="227" t="n"/>
-      <c r="J22" s="227" t="n"/>
-      <c r="K22" s="227" t="n"/>
-      <c r="L22" s="229" t="n"/>
-      <c r="M22" s="227" t="n"/>
-      <c r="N22" s="227" t="n"/>
-      <c r="O22" s="227" t="n"/>
-      <c r="P22" s="230" t="n"/>
-      <c r="Q22" s="227" t="n"/>
-      <c r="R22" s="227" t="n"/>
-      <c r="S22" s="227" t="n"/>
-      <c r="T22" s="227" t="n"/>
-      <c r="U22" s="227" t="n"/>
-      <c r="V22" s="227" t="n"/>
-      <c r="W22" s="227" t="n"/>
-      <c r="X22" s="227" t="n"/>
-      <c r="Y22" s="227" t="n"/>
-      <c r="Z22" s="227" t="n"/>
-      <c r="AA22" s="231" t="n"/>
-      <c r="AB22" s="207" t="n"/>
+      <c r="G22" s="30" t="n"/>
+      <c r="H22" s="30" t="n"/>
+      <c r="I22" s="30" t="n"/>
+      <c r="J22" s="30" t="n"/>
+      <c r="K22" s="30" t="n"/>
+      <c r="L22" s="42" t="n"/>
+      <c r="M22" s="30" t="n"/>
+      <c r="N22" s="30" t="n"/>
+      <c r="O22" s="30" t="n"/>
+      <c r="P22" s="109" t="n"/>
+      <c r="Q22" s="30" t="n"/>
+      <c r="R22" s="30" t="n"/>
+      <c r="S22" s="30" t="n"/>
+      <c r="T22" s="30" t="n"/>
+      <c r="U22" s="30" t="n"/>
+      <c r="V22" s="30" t="n"/>
+      <c r="W22" s="30" t="n"/>
+      <c r="X22" s="30" t="n"/>
+      <c r="Y22" s="30" t="n"/>
+      <c r="Z22" s="30" t="n"/>
+      <c r="AA22" s="73" t="n"/>
+      <c r="AB22" s="54" t="n"/>
     </row>
-    <row r="23" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A23" s="223" t="n"/>
-      <c r="B23" s="224" t="n"/>
+    <row r="23" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A23" s="37" t="n"/>
+      <c r="B23" s="31" t="n"/>
       <c r="C23" s="22" t="n"/>
       <c r="D23" s="16" t="n"/>
       <c r="E23" s="14" t="n"/>
       <c r="F23" s="17" t="n"/>
-      <c r="G23" s="224" t="n"/>
-      <c r="H23" s="224" t="n"/>
-      <c r="I23" s="224" t="n"/>
-      <c r="J23" s="224" t="n"/>
-      <c r="K23" s="224" t="n"/>
-      <c r="L23" s="224" t="n"/>
-      <c r="M23" s="224" t="n"/>
-      <c r="N23" s="224" t="n"/>
-      <c r="O23" s="224" t="n"/>
-      <c r="P23" s="224" t="n"/>
-      <c r="Q23" s="224" t="n"/>
-      <c r="R23" s="224" t="n"/>
-      <c r="S23" s="224" t="n"/>
-      <c r="T23" s="224" t="n"/>
-      <c r="U23" s="224" t="n"/>
-      <c r="V23" s="224" t="n"/>
-      <c r="W23" s="224" t="n"/>
-      <c r="X23" s="224" t="n"/>
-      <c r="Y23" s="224" t="n"/>
-      <c r="Z23" s="224" t="n"/>
-      <c r="AA23" s="208" t="n"/>
-      <c r="AB23" s="211" t="n"/>
+      <c r="G23" s="31" t="n"/>
+      <c r="H23" s="31" t="n"/>
+      <c r="I23" s="31" t="n"/>
+      <c r="J23" s="31" t="n"/>
+      <c r="K23" s="31" t="n"/>
+      <c r="L23" s="31" t="n"/>
+      <c r="M23" s="31" t="n"/>
+      <c r="N23" s="31" t="n"/>
+      <c r="O23" s="31" t="n"/>
+      <c r="P23" s="31" t="n"/>
+      <c r="Q23" s="31" t="n"/>
+      <c r="R23" s="31" t="n"/>
+      <c r="S23" s="31" t="n"/>
+      <c r="T23" s="31" t="n"/>
+      <c r="U23" s="31" t="n"/>
+      <c r="V23" s="31" t="n"/>
+      <c r="W23" s="31" t="n"/>
+      <c r="X23" s="31" t="n"/>
+      <c r="Y23" s="31" t="n"/>
+      <c r="Z23" s="31" t="n"/>
+      <c r="AA23" s="48" t="n"/>
+      <c r="AB23" s="55" t="n"/>
     </row>
-    <row r="24" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A24" s="225" t="n"/>
-      <c r="B24" s="233" t="n"/>
+    <row r="24" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A24" s="36" t="n"/>
+      <c r="B24" s="84" t="n"/>
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="13" t="n"/>
       <c r="E24" s="14" t="n"/>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="227" t="n"/>
-      <c r="H24" s="227" t="n"/>
-      <c r="I24" s="227" t="n"/>
-      <c r="J24" s="227" t="n"/>
-      <c r="K24" s="227" t="n"/>
-      <c r="L24" s="229" t="n"/>
-      <c r="M24" s="227" t="n"/>
-      <c r="N24" s="227" t="n"/>
-      <c r="O24" s="227" t="n"/>
-      <c r="P24" s="230" t="n"/>
-      <c r="Q24" s="227" t="n"/>
-      <c r="R24" s="227" t="n"/>
-      <c r="S24" s="227" t="n"/>
-      <c r="T24" s="227" t="n"/>
-      <c r="U24" s="227" t="n"/>
-      <c r="V24" s="227" t="n"/>
-      <c r="W24" s="227" t="n"/>
-      <c r="X24" s="227" t="n"/>
-      <c r="Y24" s="227" t="n"/>
-      <c r="Z24" s="227" t="n"/>
-      <c r="AA24" s="231" t="n"/>
-      <c r="AB24" s="207" t="n"/>
+      <c r="G24" s="30" t="n"/>
+      <c r="H24" s="30" t="n"/>
+      <c r="I24" s="30" t="n"/>
+      <c r="J24" s="30" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="42" t="n"/>
+      <c r="M24" s="30" t="n"/>
+      <c r="N24" s="30" t="n"/>
+      <c r="O24" s="30" t="n"/>
+      <c r="P24" s="109" t="n"/>
+      <c r="Q24" s="30" t="n"/>
+      <c r="R24" s="30" t="n"/>
+      <c r="S24" s="30" t="n"/>
+      <c r="T24" s="30" t="n"/>
+      <c r="U24" s="30" t="n"/>
+      <c r="V24" s="30" t="n"/>
+      <c r="W24" s="30" t="n"/>
+      <c r="X24" s="30" t="n"/>
+      <c r="Y24" s="30" t="n"/>
+      <c r="Z24" s="30" t="n"/>
+      <c r="AA24" s="73" t="n"/>
+      <c r="AB24" s="54" t="n"/>
     </row>
-    <row r="25" ht="20.25" customFormat="1" customHeight="1" s="4">
-      <c r="A25" s="223" t="n"/>
-      <c r="B25" s="224" t="n"/>
+    <row r="25" ht="20.25" customFormat="1" customHeight="1" s="44">
+      <c r="A25" s="37" t="n"/>
+      <c r="B25" s="31" t="n"/>
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="16" t="n"/>
       <c r="E25" s="14" t="n"/>
       <c r="F25" s="17" t="n"/>
-      <c r="G25" s="224" t="n"/>
-      <c r="H25" s="224" t="n"/>
-      <c r="I25" s="224" t="n"/>
-      <c r="J25" s="224" t="n"/>
-      <c r="K25" s="224" t="n"/>
-      <c r="L25" s="224" t="n"/>
-      <c r="M25" s="224" t="n"/>
-      <c r="N25" s="224" t="n"/>
-      <c r="O25" s="224" t="n"/>
-      <c r="P25" s="224" t="n"/>
-      <c r="Q25" s="224" t="n"/>
-      <c r="R25" s="224" t="n"/>
-      <c r="S25" s="224" t="n"/>
-      <c r="T25" s="224" t="n"/>
-      <c r="U25" s="224" t="n"/>
-      <c r="V25" s="224" t="n"/>
-      <c r="W25" s="224" t="n"/>
-      <c r="X25" s="224" t="n"/>
-      <c r="Y25" s="224" t="n"/>
-      <c r="Z25" s="224" t="n"/>
-      <c r="AA25" s="208" t="n"/>
-      <c r="AB25" s="211" t="n"/>
+      <c r="G25" s="31" t="n"/>
+      <c r="H25" s="31" t="n"/>
+      <c r="I25" s="31" t="n"/>
+      <c r="J25" s="31" t="n"/>
+      <c r="K25" s="31" t="n"/>
+      <c r="L25" s="31" t="n"/>
+      <c r="M25" s="31" t="n"/>
+      <c r="N25" s="31" t="n"/>
+      <c r="O25" s="31" t="n"/>
+      <c r="P25" s="31" t="n"/>
+      <c r="Q25" s="31" t="n"/>
+      <c r="R25" s="31" t="n"/>
+      <c r="S25" s="31" t="n"/>
+      <c r="T25" s="31" t="n"/>
+      <c r="U25" s="31" t="n"/>
+      <c r="V25" s="31" t="n"/>
+      <c r="W25" s="31" t="n"/>
+      <c r="X25" s="31" t="n"/>
+      <c r="Y25" s="31" t="n"/>
+      <c r="Z25" s="31" t="n"/>
+      <c r="AA25" s="48" t="n"/>
+      <c r="AB25" s="55" t="n"/>
     </row>
-    <row r="26" ht="18" customFormat="1" customHeight="1" s="94">
-      <c r="A26" s="234" t="inlineStr">
+    <row r="26" ht="18" customFormat="1" customHeight="1" s="40">
+      <c r="A26" s="99" t="inlineStr">
         <is>
           <t>① 0:ORIGINAL 용접부 R:REPAIR용접부 GR:GRINDING용접부 CL:CLEANING용접부</t>
         </is>
       </c>
-      <c r="B26" s="203" t="n"/>
-      <c r="C26" s="203" t="n"/>
-      <c r="D26" s="203" t="n"/>
-      <c r="E26" s="203" t="n"/>
-      <c r="F26" s="203" t="n"/>
-      <c r="G26" s="203" t="n"/>
-      <c r="H26" s="203" t="n"/>
-      <c r="I26" s="203" t="n"/>
-      <c r="J26" s="201" t="n"/>
-      <c r="K26" s="227" t="inlineStr">
+      <c r="B26" s="45" t="n"/>
+      <c r="C26" s="45" t="n"/>
+      <c r="D26" s="45" t="n"/>
+      <c r="E26" s="45" t="n"/>
+      <c r="F26" s="45" t="n"/>
+      <c r="G26" s="45" t="n"/>
+      <c r="H26" s="45" t="n"/>
+      <c r="I26" s="45" t="n"/>
+      <c r="J26" s="46" t="n"/>
+      <c r="K26" s="30" t="inlineStr">
         <is>
           <t>비 고</t>
         </is>
       </c>
-      <c r="L26" s="235" t="inlineStr">
+      <c r="L26" s="80" t="inlineStr">
         <is>
           <t>시공감리:63,64</t>
         </is>
       </c>
-      <c r="M26" s="203" t="n"/>
-      <c r="N26" s="203" t="n"/>
-      <c r="O26" s="203" t="n"/>
-      <c r="P26" s="203" t="n"/>
-      <c r="Q26" s="203" t="n"/>
-      <c r="R26" s="203" t="n"/>
-      <c r="S26" s="203" t="n"/>
-      <c r="T26" s="201" t="n"/>
-      <c r="U26" s="227" t="inlineStr">
+      <c r="M26" s="45" t="n"/>
+      <c r="N26" s="45" t="n"/>
+      <c r="O26" s="45" t="n"/>
+      <c r="P26" s="45" t="n"/>
+      <c r="Q26" s="45" t="n"/>
+      <c r="R26" s="45" t="n"/>
+      <c r="S26" s="45" t="n"/>
+      <c r="T26" s="46" t="n"/>
+      <c r="U26" s="30" t="inlineStr">
         <is>
           <t>검 토 자</t>
         </is>
       </c>
-      <c r="V26" s="203" t="n"/>
-      <c r="W26" s="201" t="n"/>
-      <c r="X26" s="236" t="n"/>
-      <c r="Y26" s="203" t="n"/>
-      <c r="Z26" s="203" t="n"/>
-      <c r="AA26" s="203" t="n"/>
-      <c r="AB26" s="207" t="n"/>
+      <c r="V26" s="45" t="n"/>
+      <c r="W26" s="46" t="n"/>
+      <c r="X26" s="69" t="n"/>
+      <c r="Y26" s="45" t="n"/>
+      <c r="Z26" s="45" t="n"/>
+      <c r="AA26" s="45" t="n"/>
+      <c r="AB26" s="54" t="n"/>
       <c r="AC26" s="23" t="n"/>
     </row>
-    <row r="27" ht="18" customFormat="1" customHeight="1" s="94">
-      <c r="A27" s="237" t="inlineStr">
+    <row r="27" ht="18" customFormat="1" customHeight="1" s="40">
+      <c r="A27" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">   C:절단된 용접부 A:추가 지정된 용접부</t>
         </is>
       </c>
-      <c r="B27" s="190" t="n"/>
-      <c r="C27" s="190" t="n"/>
-      <c r="D27" s="190" t="n"/>
-      <c r="E27" s="190" t="n"/>
-      <c r="F27" s="190" t="n"/>
-      <c r="G27" s="190" t="n"/>
-      <c r="H27" s="190" t="n"/>
-      <c r="I27" s="190" t="n"/>
-      <c r="J27" s="191" t="n"/>
-      <c r="K27" s="218" t="n"/>
-      <c r="L27" s="238" t="n"/>
-      <c r="T27" s="210" t="n"/>
-      <c r="U27" s="209" t="n"/>
-      <c r="W27" s="210" t="n"/>
-      <c r="X27" s="209" t="n"/>
-      <c r="AB27" s="219" t="n"/>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="49" t="n"/>
+      <c r="J27" s="50" t="n"/>
+      <c r="K27" s="34" t="n"/>
+      <c r="L27" s="39" t="n"/>
+      <c r="T27" s="41" t="n"/>
+      <c r="U27" s="47" t="n"/>
+      <c r="W27" s="41" t="n"/>
+      <c r="X27" s="47" t="n"/>
+      <c r="AB27" s="64" t="n"/>
       <c r="AC27" s="23" t="n"/>
     </row>
-    <row r="28" ht="18" customFormat="1" customHeight="1" s="94">
-      <c r="A28" s="239" t="inlineStr">
+    <row r="28" ht="18" customFormat="1" customHeight="1" s="40">
+      <c r="A28" s="58" t="inlineStr">
         <is>
           <t>② 시공계약자 용접검사: 시공계약자가 현장 확인후 서명</t>
         </is>
       </c>
-      <c r="B28" s="192" t="n"/>
-      <c r="C28" s="192" t="n"/>
-      <c r="D28" s="192" t="n"/>
-      <c r="E28" s="192" t="n"/>
-      <c r="F28" s="192" t="n"/>
-      <c r="G28" s="192" t="n"/>
-      <c r="H28" s="192" t="n"/>
-      <c r="I28" s="192" t="n"/>
-      <c r="J28" s="198" t="n"/>
-      <c r="K28" s="218" t="n"/>
-      <c r="L28" s="240" t="n"/>
-      <c r="T28" s="210" t="n"/>
-      <c r="U28" s="208" t="n"/>
-      <c r="V28" s="190" t="n"/>
-      <c r="W28" s="191" t="n"/>
-      <c r="X28" s="208" t="n"/>
-      <c r="Y28" s="190" t="n"/>
-      <c r="Z28" s="190" t="n"/>
-      <c r="AA28" s="190" t="n"/>
-      <c r="AB28" s="211" t="n"/>
+      <c r="B28" s="59" t="n"/>
+      <c r="C28" s="59" t="n"/>
+      <c r="D28" s="59" t="n"/>
+      <c r="E28" s="59" t="n"/>
+      <c r="F28" s="59" t="n"/>
+      <c r="G28" s="59" t="n"/>
+      <c r="H28" s="59" t="n"/>
+      <c r="I28" s="59" t="n"/>
+      <c r="J28" s="60" t="n"/>
+      <c r="K28" s="34" t="n"/>
+      <c r="L28" s="98" t="n"/>
+      <c r="T28" s="41" t="n"/>
+      <c r="U28" s="48" t="n"/>
+      <c r="V28" s="49" t="n"/>
+      <c r="W28" s="50" t="n"/>
+      <c r="X28" s="48" t="n"/>
+      <c r="Y28" s="49" t="n"/>
+      <c r="Z28" s="49" t="n"/>
+      <c r="AA28" s="49" t="n"/>
+      <c r="AB28" s="55" t="n"/>
       <c r="AC28" s="23" t="n"/>
     </row>
-    <row r="29" ht="18" customFormat="1" customHeight="1" s="94">
-      <c r="A29" s="239" t="inlineStr">
+    <row r="29" ht="18" customFormat="1" customHeight="1" s="40">
+      <c r="A29" s="58" t="inlineStr">
         <is>
           <t>③ 시공감독확인 : R(시공계약자 검사사항 검토). W(현장입회 확인)</t>
         </is>
       </c>
-      <c r="B29" s="192" t="n"/>
-      <c r="C29" s="192" t="n"/>
-      <c r="D29" s="192" t="n"/>
-      <c r="E29" s="192" t="n"/>
-      <c r="F29" s="192" t="n"/>
-      <c r="G29" s="192" t="n"/>
-      <c r="H29" s="192" t="n"/>
-      <c r="I29" s="192" t="n"/>
-      <c r="J29" s="198" t="n"/>
-      <c r="K29" s="218" t="n"/>
-      <c r="L29" s="238" t="n"/>
-      <c r="T29" s="210" t="n"/>
-      <c r="U29" s="227" t="inlineStr">
+      <c r="B29" s="59" t="n"/>
+      <c r="C29" s="59" t="n"/>
+      <c r="D29" s="59" t="n"/>
+      <c r="E29" s="59" t="n"/>
+      <c r="F29" s="59" t="n"/>
+      <c r="G29" s="59" t="n"/>
+      <c r="H29" s="59" t="n"/>
+      <c r="I29" s="59" t="n"/>
+      <c r="J29" s="60" t="n"/>
+      <c r="K29" s="34" t="n"/>
+      <c r="L29" s="39" t="n"/>
+      <c r="T29" s="41" t="n"/>
+      <c r="U29" s="30" t="inlineStr">
         <is>
           <t>검토일자</t>
         </is>
       </c>
-      <c r="V29" s="203" t="n"/>
-      <c r="W29" s="201" t="n"/>
-      <c r="X29" s="241">
+      <c r="V29" s="45" t="n"/>
+      <c r="W29" s="46" t="n"/>
+      <c r="X29" s="111">
         <f>L5</f>
         <v/>
       </c>
-      <c r="Y29" s="203" t="n"/>
-      <c r="Z29" s="203" t="n"/>
-      <c r="AA29" s="203" t="n"/>
-      <c r="AB29" s="207" t="n"/>
+      <c r="Y29" s="45" t="n"/>
+      <c r="Z29" s="45" t="n"/>
+      <c r="AA29" s="45" t="n"/>
+      <c r="AB29" s="54" t="n"/>
       <c r="AC29" s="23" t="n"/>
     </row>
-    <row r="30" ht="18" customFormat="1" customHeight="1" s="94">
-      <c r="A30" s="242" t="inlineStr">
+    <row r="30" ht="18" customFormat="1" customHeight="1" s="40">
+      <c r="A30" s="83" t="inlineStr">
         <is>
           <t>④ 필름번호 : 1.2.3.4.5.6.7 →[1→2].[2→3].[3→4].[4→5].[5→6].[6→7].[7→1]</t>
         </is>
       </c>
-      <c r="B30" s="192" t="n"/>
-      <c r="C30" s="192" t="n"/>
-      <c r="D30" s="192" t="n"/>
-      <c r="E30" s="192" t="n"/>
-      <c r="F30" s="192" t="n"/>
-      <c r="G30" s="192" t="n"/>
-      <c r="H30" s="192" t="n"/>
-      <c r="I30" s="192" t="n"/>
-      <c r="J30" s="198" t="n"/>
-      <c r="K30" s="224" t="n"/>
-      <c r="L30" s="243" t="n"/>
-      <c r="M30" s="190" t="n"/>
-      <c r="N30" s="190" t="n"/>
-      <c r="O30" s="190" t="n"/>
-      <c r="P30" s="190" t="n"/>
-      <c r="Q30" s="190" t="n"/>
-      <c r="R30" s="190" t="n"/>
-      <c r="S30" s="190" t="n"/>
-      <c r="T30" s="191" t="n"/>
-      <c r="U30" s="208" t="n"/>
-      <c r="V30" s="190" t="n"/>
-      <c r="W30" s="191" t="n"/>
-      <c r="X30" s="208" t="n"/>
-      <c r="Y30" s="190" t="n"/>
-      <c r="Z30" s="190" t="n"/>
-      <c r="AA30" s="190" t="n"/>
-      <c r="AB30" s="211" t="n"/>
+      <c r="B30" s="59" t="n"/>
+      <c r="C30" s="59" t="n"/>
+      <c r="D30" s="59" t="n"/>
+      <c r="E30" s="59" t="n"/>
+      <c r="F30" s="59" t="n"/>
+      <c r="G30" s="59" t="n"/>
+      <c r="H30" s="59" t="n"/>
+      <c r="I30" s="59" t="n"/>
+      <c r="J30" s="60" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="62" t="n"/>
+      <c r="M30" s="49" t="n"/>
+      <c r="N30" s="49" t="n"/>
+      <c r="O30" s="49" t="n"/>
+      <c r="P30" s="49" t="n"/>
+      <c r="Q30" s="49" t="n"/>
+      <c r="R30" s="49" t="n"/>
+      <c r="S30" s="49" t="n"/>
+      <c r="T30" s="50" t="n"/>
+      <c r="U30" s="48" t="n"/>
+      <c r="V30" s="49" t="n"/>
+      <c r="W30" s="50" t="n"/>
+      <c r="X30" s="48" t="n"/>
+      <c r="Y30" s="49" t="n"/>
+      <c r="Z30" s="49" t="n"/>
+      <c r="AA30" s="49" t="n"/>
+      <c r="AB30" s="55" t="n"/>
       <c r="AC30" s="23" t="n"/>
     </row>
-    <row r="31" ht="26.25" customFormat="1" customHeight="1" s="94" thickBot="1">
+    <row r="31" ht="26.25" customFormat="1" customHeight="1" s="40" thickBot="1">
       <c r="A31" s="24" t="n"/>
       <c r="B31" s="25" t="n"/>
       <c r="C31" s="25" t="n"/>
@@ -3745,19 +3348,19 @@
       <c r="T31" s="27" t="n"/>
       <c r="U31" s="27" t="n"/>
       <c r="V31" s="27" t="n"/>
-      <c r="W31" s="49" t="inlineStr">
+      <c r="W31" s="88" t="inlineStr">
         <is>
           <t>A4(297X210mm)</t>
         </is>
       </c>
-      <c r="X31" s="244" t="n"/>
-      <c r="Y31" s="244" t="n"/>
-      <c r="Z31" s="244" t="n"/>
-      <c r="AA31" s="244" t="n"/>
-      <c r="AB31" s="245" t="n"/>
+      <c r="X31" s="89" t="n"/>
+      <c r="Y31" s="89" t="n"/>
+      <c r="Z31" s="89" t="n"/>
+      <c r="AA31" s="89" t="n"/>
+      <c r="AB31" s="90" t="n"/>
       <c r="AC31" s="28" t="n"/>
     </row>
-    <row r="32" ht="19.5" customFormat="1" customHeight="1" s="94">
+    <row r="32" ht="19.5" customFormat="1" customHeight="1" s="40">
       <c r="A32" s="29" t="n"/>
       <c r="B32" s="29" t="n"/>
       <c r="C32" s="29" t="n"/>
@@ -3903,8 +3506,8 @@
     <mergeCell ref="Q7:W7"/>
     <mergeCell ref="J24:J25"/>
     <mergeCell ref="A30:J30"/>
+    <mergeCell ref="R20:R21"/>
     <mergeCell ref="AA18:AB19"/>
-    <mergeCell ref="R20:R21"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="X18:X19"/>
     <mergeCell ref="G9:G13"/>
@@ -3931,9 +3534,9 @@
     <mergeCell ref="H20:H21"/>
     <mergeCell ref="K16:K17"/>
     <mergeCell ref="T20:T21"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="K18:K19"/>
     <mergeCell ref="V20:V21"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="Q24:Q25"/>
     <mergeCell ref="V14:V15"/>
     <mergeCell ref="S18:S19"/>
     <mergeCell ref="A24:A25"/>
@@ -3956,8 +3559,8 @@
     <mergeCell ref="M22:M23"/>
     <mergeCell ref="W22:W23"/>
     <mergeCell ref="I9:I13"/>
+    <mergeCell ref="Y22:Y23"/>
     <mergeCell ref="M16:M17"/>
-    <mergeCell ref="Y22:Y23"/>
     <mergeCell ref="V2:AB2"/>
     <mergeCell ref="P16:P17"/>
     <mergeCell ref="A18:A19"/>
@@ -3972,12 +3575,12 @@
     <mergeCell ref="K14:K15"/>
     <mergeCell ref="O9:O13"/>
     <mergeCell ref="U14:U15"/>
+    <mergeCell ref="W14:W15"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="L27:T27"/>
     <mergeCell ref="V16:V17"/>
     <mergeCell ref="C5:D6"/>
-    <mergeCell ref="L27:T27"/>
+    <mergeCell ref="R18:R19"/>
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="AP17:AP18"/>
     <mergeCell ref="K9:K13"/>
